--- a/output/pdf_financials_xlsx/BNZ.xlsx
+++ b/output/pdf_financials_xlsx/BNZ.xlsx
@@ -4587,10 +4587,10 @@
         <v>0.379502</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.268951</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.289351</v>
       </c>
     </row>
     <row r="93">
@@ -5682,19 +5682,19 @@
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.002867</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.312562</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-1.087384</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.058351</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.008359</v>
       </c>
       <c r="L118" s="3" t="n">
         <v>0</v>
@@ -7298,7 +7298,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -18116,7 +18120,11 @@
           <t>Deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BNZ.xlsx
+++ b/output/pdf_financials_xlsx/BNZ.xlsx
@@ -891,28 +891,28 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003745</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.007197</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.007548</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.006294</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.005291</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001229</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1623,28 +1623,28 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.203016</v>
+        <v>-0.206761</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.10745</v>
+        <v>-0.114647</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.139362</v>
+        <v>-0.14691</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.073004</v>
+        <v>-0.075504</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-4.694072</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.112712</v>
+        <v>-0.119006</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.177281</v>
+        <v>-0.182572</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.146507</v>
+        <v>-0.147736</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.184065</v>
@@ -1711,28 +1711,28 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.203016</v>
+        <v>-0.206761</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.10745</v>
+        <v>-0.114647</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.139362</v>
+        <v>-0.14691</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.073004</v>
+        <v>-0.075504</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-4.694072</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.112712</v>
+        <v>-0.119006</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.177281</v>
+        <v>-0.182572</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.146507</v>
+        <v>-0.147736</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.184065</v>
@@ -1939,22 +1939,22 @@
         <v>0.619179</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.823759</v>
+        <v>0.145759</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.316966</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.248342</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.048115</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.091145</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.152353</v>
       </c>
     </row>
     <row r="35">
@@ -2027,22 +2027,22 @@
         <v>0.619179</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.823759</v>
+        <v>0.145759</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.316966</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.248342</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.048115</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.091145</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.152353</v>
       </c>
     </row>
     <row r="37">
@@ -2555,22 +2555,22 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0</v>
+        <v>0.009554</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.362788</v>
+        <v>0.045822</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.266187</v>
+        <v>0.017845</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.054446</v>
+        <v>0.006331</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.097723</v>
+        <v>0.006578</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.165662</v>
+        <v>0.013309</v>
       </c>
     </row>
     <row r="49">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6853,7 +6853,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -12396,7 +12400,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -18859,7 +18867,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -21797,7 +21809,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -24049,7 +24061,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">

--- a/output/pdf_financials_xlsx/BNZ.xlsx
+++ b/output/pdf_financials_xlsx/BNZ.xlsx
@@ -18727,7 +18727,11 @@
           <t>Units/shares issued for cash</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -19484,7 +19488,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -19618,7 +19626,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -22925,7 +22937,11 @@
           <t>Deferred income tax recovery 12</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
